--- a/VCEM_4_0/input/disk_compression_data.xlsx
+++ b/VCEM_4_0/input/disk_compression_data.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Fracture\VCEM_4_0\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3280444E-2B39-47E7-81F5-096C289D53D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BF4451-31F7-4991-BCC8-9051842C02C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BEM" sheetId="1" r:id="rId1"/>
     <sheet name="GEOMETRY" sheetId="2" r:id="rId2"/>
-    <sheet name="CRACK_NETWORK" sheetId="3" r:id="rId3"/>
+    <sheet name="CRACK_NETWORK" sheetId="6" r:id="rId3"/>
     <sheet name="CONFIGURATION_LOGIC" sheetId="4" r:id="rId4"/>
     <sheet name="CONFIGURATION_PARAM" sheetId="5" r:id="rId5"/>
+    <sheet name="CRACK_NETWORK_RANDOM_1" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="175">
   <si>
     <t>id</t>
   </si>
@@ -62,9 +63,6 @@
     <t>P_total_N</t>
   </si>
   <si>
-    <t>Total compressive force per platen [N]</t>
-  </si>
-  <si>
     <t>E_Pa</t>
   </si>
   <si>
@@ -113,9 +111,6 @@
     <t>boundary_mesh</t>
   </si>
   <si>
-    <t>uniform</t>
-  </si>
-  <si>
     <t>Boundary-node distribution on the outer circle. 'clustered' concentrates nodes at the +/-90 deg platens and tapers toward the equator.</t>
   </si>
   <si>
@@ -263,9 +258,6 @@
     <t>output_dir_name</t>
   </si>
   <si>
-    <t>BEM_Brazilian_disk_iterative</t>
-  </si>
-  <si>
     <t>Subdir name under repo_root/output/</t>
   </si>
   <si>
@@ -293,9 +285,6 @@
     <t>solver_kwargs.parametrization</t>
   </si>
   <si>
-    <t>polyline</t>
-  </si>
-  <si>
     <t>Per-polyline geometry the BEM solver assumes. 'polyline' keeps piecewise-linear segments with kink refinement at every interior vertex. 'cspline' fits a natural cubic spline (heavier; kept for opt-in experiments).</t>
   </si>
   <si>
@@ -317,9 +306,6 @@
     <t>solver_kwargs.junction_model</t>
   </si>
   <si>
-    <t>strict</t>
-  </si>
-  <si>
     <t>Junction DOF model (used only when crack_mode='half'). 'strict' shares one jump DOF per junction vertex (smallest column count). 'core' allocates per-branch-end DOFs with hard continuity rows in C. 'soft' appends weighted-LS continuity rows to K instead of C (no column-rank deficit, best conditioning).</t>
   </si>
   <si>
@@ -546,6 +532,24 @@
   </si>
   <si>
     <t>Figure DPI</t>
+  </si>
+  <si>
+    <t>single_pass</t>
+  </si>
+  <si>
+    <t>cspline</t>
+  </si>
+  <si>
+    <t>soft</t>
+  </si>
+  <si>
+    <t>clustered</t>
+  </si>
+  <si>
+    <t>vertical_branched</t>
+  </si>
+  <si>
+    <t>Total compressive force per platen [N] -default 3800</t>
   </si>
 </sst>
 </file>
@@ -951,148 +955,148 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>3800</v>
+        <v>10000</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>231520000000</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>0.3</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>6.3499999999999997E-3</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14">
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1125,126 +1129,126 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>41</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>1.2699999999999999E-2</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
         <v>52</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>53</v>
-      </c>
-      <c r="C7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>0.03</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B10">
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B11">
         <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1253,8 +1257,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88629301-9A28-45BD-B46B-75013A3D607A}">
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1279,10 +1283,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>-1.1024673514458631E-2</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>-3.018977838005418E-3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1296,574 +1300,48 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>-1.087985178336567E-2</v>
-      </c>
-      <c r="C3">
-        <v>-2.8200267592871781E-3</v>
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-5.0000000000000001E-3</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>2</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>-6.1630830463504788E-3</v>
-      </c>
-      <c r="C4">
-        <v>3.8494094806253729E-4</v>
+      <c r="B4" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>-7.3737718095974606E-3</v>
-      </c>
-      <c r="C5">
-        <v>8.2301751222427027E-4</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>4.0846385912184993E-3</v>
-      </c>
-      <c r="C6">
-        <v>5.3306991455441786E-3</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>4.2100908668257549E-3</v>
-      </c>
-      <c r="C7">
-        <v>6.1282762180874754E-3</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>-1.1999949593368401E-2</v>
-      </c>
-      <c r="C8">
-        <v>-3.2718143821980572E-4</v>
-      </c>
-      <c r="E8">
-        <v>12</v>
-      </c>
-      <c r="F8">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>-1.1839613170649139E-2</v>
-      </c>
-      <c r="C9">
-        <v>3.4278734048728609E-4</v>
-      </c>
-      <c r="E9">
-        <v>14</v>
-      </c>
-      <c r="F9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>3.59321370540796E-3</v>
-      </c>
-      <c r="C10">
-        <v>-1.2733196265123201E-3</v>
-      </c>
-      <c r="E10">
-        <v>16</v>
-      </c>
-      <c r="F10">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>-1.6554434016597609E-3</v>
-      </c>
-      <c r="C11">
-        <v>-9.6288071650121963E-4</v>
-      </c>
-      <c r="E11">
-        <v>18</v>
-      </c>
-      <c r="F11">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>-5.4863210620815183E-4</v>
-      </c>
-      <c r="C12">
-        <v>-2.0241494810429189E-3</v>
-      </c>
-      <c r="E12">
-        <v>20</v>
-      </c>
-      <c r="F12">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>-2.411822451171295E-4</v>
-      </c>
-      <c r="C13">
-        <v>-2.0086903452366371E-3</v>
-      </c>
-      <c r="E13">
-        <v>22</v>
-      </c>
-      <c r="F13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>3.3438695984570801E-3</v>
-      </c>
-      <c r="C14">
-        <v>-8.5336776090966272E-3</v>
-      </c>
-      <c r="E14">
-        <v>24</v>
-      </c>
-      <c r="F14">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <v>3.3115633287274459E-3</v>
-      </c>
-      <c r="C15">
-        <v>-8.3656872880119235E-3</v>
-      </c>
-      <c r="E15">
-        <v>26</v>
-      </c>
-      <c r="F15">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <v>-9.595816006284486E-4</v>
-      </c>
-      <c r="C16">
-        <v>8.7389709885425475E-4</v>
-      </c>
-      <c r="E16">
-        <v>28</v>
-      </c>
-      <c r="F16">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17">
-        <v>-6.508786765101074E-4</v>
-      </c>
-      <c r="C17">
-        <v>9.5174388939840411E-4</v>
-      </c>
-      <c r="E17">
-        <v>30</v>
-      </c>
-      <c r="F17">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18">
-        <v>-4.8103910200200184E-3</v>
-      </c>
-      <c r="C18">
-        <v>7.2316492195925487E-3</v>
-      </c>
-      <c r="E18">
-        <v>32</v>
-      </c>
-      <c r="F18">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19">
-        <v>-4.9268280086337771E-3</v>
-      </c>
-      <c r="C19">
-        <v>7.2335085994043487E-3</v>
-      </c>
-      <c r="E19">
-        <v>34</v>
-      </c>
-      <c r="F19">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20">
-        <v>-8.4770647625855358E-3</v>
-      </c>
-      <c r="C20">
-        <v>-4.6139746744436267E-3</v>
-      </c>
-      <c r="E20">
-        <v>36</v>
-      </c>
-      <c r="F20">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21">
-        <v>-7.6348821152110299E-3</v>
-      </c>
-      <c r="C21">
-        <v>-4.0255119292708606E-3</v>
-      </c>
-      <c r="E21">
-        <v>38</v>
-      </c>
-      <c r="F21">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22">
-        <v>-3.1513145945869249E-3</v>
-      </c>
-      <c r="C22">
-        <v>-1.3260289837763241E-4</v>
-      </c>
-      <c r="E22">
-        <v>40</v>
-      </c>
-      <c r="F22">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23">
-        <v>-3.4079420120282119E-3</v>
-      </c>
-      <c r="C23">
-        <v>1.3372291761812739E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24">
-        <v>4.5121639088053309E-3</v>
-      </c>
-      <c r="C24">
-        <v>7.2469540553818258E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>4.3754509538804862E-3</v>
-      </c>
-      <c r="C25">
-        <v>7.4720549354657349E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>-4.2173695201039247E-3</v>
-      </c>
-      <c r="C26">
-        <v>-8.1446304704004633E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27">
-        <v>-6.4193647155283739E-3</v>
-      </c>
-      <c r="C27">
-        <v>-7.5324868993483099E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28">
-        <v>-6.0722518487118984E-3</v>
-      </c>
-      <c r="C28">
-        <v>1.3069706088957021E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29">
-        <v>-6.6828387795839876E-3</v>
-      </c>
-      <c r="C29">
-        <v>5.9739170062547654E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30">
-        <v>5.54994643730244E-3</v>
-      </c>
-      <c r="C30">
-        <v>-6.3993404836109637E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31">
-        <v>5.4878117019380611E-3</v>
-      </c>
-      <c r="C31">
-        <v>-6.3146996306464552E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32">
-        <v>-5.7212525790471119E-4</v>
-      </c>
-      <c r="C32">
-        <v>-2.439661709310655E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33">
-        <v>-6.0045791711510433E-4</v>
-      </c>
-      <c r="C33">
-        <v>-2.3110612562413789E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="B34">
-        <v>-1.630249041606551E-3</v>
-      </c>
-      <c r="C34">
-        <v>-4.1130170832092486E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="B35">
-        <v>-7.4485857738666099E-4</v>
-      </c>
-      <c r="C35">
-        <v>-2.6373331100384241E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36">
-        <v>-6.1631317920284113E-3</v>
-      </c>
-      <c r="C36">
-        <v>-8.5141941171588114E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="B37">
-        <v>-6.3904357863606718E-3</v>
-      </c>
-      <c r="C37">
-        <v>-7.8910680336036539E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="B38">
-        <v>-1.142442613277634E-3</v>
-      </c>
-      <c r="C38">
-        <v>8.2262143920355593E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="B39">
-        <v>4.9169889910811733E-4</v>
-      </c>
-      <c r="C39">
-        <v>8.6058447620078402E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="B40">
-        <v>4.9295322137345807E-3</v>
-      </c>
-      <c r="C40">
-        <v>-1.890711666694784E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="B41">
-        <v>5.1834727551334208E-3</v>
-      </c>
-      <c r="C41">
-        <v>-1.7484250509056051E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="B42">
+      <c r="B5" s="2">
         <v>-1E-3</v>
       </c>
-      <c r="C42">
-        <v>-4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>2E-3</v>
+      <c r="C5" s="2">
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1894,349 +1372,349 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
         <v>66</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
         <v>70</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B4" t="b">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B5" t="b">
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B8" t="b">
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B14" t="b">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B15" t="b">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B16" t="b">
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B17" t="b">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B18" t="b">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B19" t="b">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B21" t="b">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B22" t="b">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B23" t="b">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B24" t="b">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B25" t="b">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B26" t="b">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2271,233 +1749,848 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B2">
         <v>30</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B3">
         <v>1000</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B4">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B5" s="2">
         <v>3000000</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B6">
         <v>0.25</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B7">
         <v>8</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B8">
         <v>20</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B9">
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B10">
         <v>0.4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B12">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B13">
         <v>40</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B16">
         <v>1E-4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B17">
         <v>1E-8</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B18">
         <v>97</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B20">
         <v>60</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B22">
         <v>300</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>-1.1024673514458631E-2</v>
+      </c>
+      <c r="C2">
+        <v>-3.018977838005418E-3</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>-1.087985178336567E-2</v>
+      </c>
+      <c r="C3">
+        <v>-2.8200267592871781E-3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>-6.1630830463504788E-3</v>
+      </c>
+      <c r="C4">
+        <v>3.8494094806253729E-4</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>-7.3737718095974606E-3</v>
+      </c>
+      <c r="C5">
+        <v>8.2301751222427027E-4</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4.0846385912184993E-3</v>
+      </c>
+      <c r="C6">
+        <v>5.3306991455441786E-3</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>4.2100908668257549E-3</v>
+      </c>
+      <c r="C7">
+        <v>6.1282762180874754E-3</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>-1.1999949593368401E-2</v>
+      </c>
+      <c r="C8">
+        <v>-3.2718143821980572E-4</v>
+      </c>
+      <c r="E8">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>-1.1839613170649139E-2</v>
+      </c>
+      <c r="C9">
+        <v>3.4278734048728609E-4</v>
+      </c>
+      <c r="E9">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>3.59321370540796E-3</v>
+      </c>
+      <c r="C10">
+        <v>-1.2733196265123201E-3</v>
+      </c>
+      <c r="E10">
+        <v>16</v>
+      </c>
+      <c r="F10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>-1.6554434016597609E-3</v>
+      </c>
+      <c r="C11">
+        <v>-9.6288071650121963E-4</v>
+      </c>
+      <c r="E11">
+        <v>18</v>
+      </c>
+      <c r="F11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>-5.4863210620815183E-4</v>
+      </c>
+      <c r="C12">
+        <v>-2.0241494810429189E-3</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>-2.411822451171295E-4</v>
+      </c>
+      <c r="C13">
+        <v>-2.0086903452366371E-3</v>
+      </c>
+      <c r="E13">
+        <v>22</v>
+      </c>
+      <c r="F13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>3.3438695984570801E-3</v>
+      </c>
+      <c r="C14">
+        <v>-8.5336776090966272E-3</v>
+      </c>
+      <c r="E14">
+        <v>24</v>
+      </c>
+      <c r="F14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>3.3115633287274459E-3</v>
+      </c>
+      <c r="C15">
+        <v>-8.3656872880119235E-3</v>
+      </c>
+      <c r="E15">
+        <v>26</v>
+      </c>
+      <c r="F15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>-9.595816006284486E-4</v>
+      </c>
+      <c r="C16">
+        <v>8.7389709885425475E-4</v>
+      </c>
+      <c r="E16">
+        <v>28</v>
+      </c>
+      <c r="F16">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>-6.508786765101074E-4</v>
+      </c>
+      <c r="C17">
+        <v>9.5174388939840411E-4</v>
+      </c>
+      <c r="E17">
+        <v>30</v>
+      </c>
+      <c r="F17">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>-4.8103910200200184E-3</v>
+      </c>
+      <c r="C18">
+        <v>7.2316492195925487E-3</v>
+      </c>
+      <c r="E18">
+        <v>32</v>
+      </c>
+      <c r="F18">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>-4.9268280086337771E-3</v>
+      </c>
+      <c r="C19">
+        <v>7.2335085994043487E-3</v>
+      </c>
+      <c r="E19">
+        <v>34</v>
+      </c>
+      <c r="F19">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>-8.4770647625855358E-3</v>
+      </c>
+      <c r="C20">
+        <v>-4.6139746744436267E-3</v>
+      </c>
+      <c r="E20">
+        <v>36</v>
+      </c>
+      <c r="F20">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>-7.6348821152110299E-3</v>
+      </c>
+      <c r="C21">
+        <v>-4.0255119292708606E-3</v>
+      </c>
+      <c r="E21">
+        <v>38</v>
+      </c>
+      <c r="F21">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>-3.1513145945869249E-3</v>
+      </c>
+      <c r="C22">
+        <v>-1.3260289837763241E-4</v>
+      </c>
+      <c r="E22">
+        <v>40</v>
+      </c>
+      <c r="F22">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>-3.4079420120282119E-3</v>
+      </c>
+      <c r="C23">
+        <v>1.3372291761812739E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>4.5121639088053309E-3</v>
+      </c>
+      <c r="C24">
+        <v>7.2469540553818258E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>4.3754509538804862E-3</v>
+      </c>
+      <c r="C25">
+        <v>7.4720549354657349E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>-4.2173695201039247E-3</v>
+      </c>
+      <c r="C26">
+        <v>-8.1446304704004633E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>-6.4193647155283739E-3</v>
+      </c>
+      <c r="C27">
+        <v>-7.5324868993483099E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>-6.0722518487118984E-3</v>
+      </c>
+      <c r="C28">
+        <v>1.3069706088957021E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>-6.6828387795839876E-3</v>
+      </c>
+      <c r="C29">
+        <v>5.9739170062547654E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>5.54994643730244E-3</v>
+      </c>
+      <c r="C30">
+        <v>-6.3993404836109637E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>5.4878117019380611E-3</v>
+      </c>
+      <c r="C31">
+        <v>-6.3146996306464552E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>-5.7212525790471119E-4</v>
+      </c>
+      <c r="C32">
+        <v>-2.439661709310655E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>-6.0045791711510433E-4</v>
+      </c>
+      <c r="C33">
+        <v>-2.3110612562413789E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>-1.630249041606551E-3</v>
+      </c>
+      <c r="C34">
+        <v>-4.1130170832092486E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>-7.4485857738666099E-4</v>
+      </c>
+      <c r="C35">
+        <v>-2.6373331100384241E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>-6.1631317920284113E-3</v>
+      </c>
+      <c r="C36">
+        <v>-8.5141941171588114E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>-6.3904357863606718E-3</v>
+      </c>
+      <c r="C37">
+        <v>-7.8910680336036539E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>-1.142442613277634E-3</v>
+      </c>
+      <c r="C38">
+        <v>8.2262143920355593E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>4.9169889910811733E-4</v>
+      </c>
+      <c r="C39">
+        <v>8.6058447620078402E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>4.9295322137345807E-3</v>
+      </c>
+      <c r="C40">
+        <v>-1.890711666694784E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>5.1834727551334208E-3</v>
+      </c>
+      <c r="C41">
+        <v>-1.7484250509056051E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>-1E-3</v>
+      </c>
+      <c r="C42">
+        <v>-4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>2E-3</v>
       </c>
     </row>
   </sheetData>
